--- a/abril-2026.xlsx
+++ b/abril-2026.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A7431BE8-1DDF-4EE5-A5D6-05E16C98204A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85F17DC-2C7B-4E09-B080-46A3A5CADAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet0" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet0" sheetId="2" r:id="rId1"/>
+    <sheet name="Abril" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>Contrato</t>
   </si>
@@ -152,6 +153,150 @@
   </si>
   <si>
     <t xml:space="preserve">       4519291,75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        800319,48</t>
+  </si>
+  <si>
+    <t>23/07/2026</t>
+  </si>
+  <si>
+    <t>24/07/2025</t>
+  </si>
+  <si>
+    <t>PRESTAÇÃO DE SERVIÇOS DE ENGENHARIA PARA ASSESSORIA E CONSULTORIA NAS ÁREAS DE GESTÃO DOS RESÍDUOS SÓLIDOS E MEIO AMBIENTE</t>
+  </si>
+  <si>
+    <t>WMX SOLUCOES AMBIENTAIS TECNOLOGICAS LTDA</t>
+  </si>
+  <si>
+    <t>00000007/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        204575,27</t>
+  </si>
+  <si>
+    <t>13/07/2026</t>
+  </si>
+  <si>
+    <t>14/07/2025</t>
+  </si>
+  <si>
+    <t>MANUTENÇÃO PREVENTIVA E CORRETIVA EM DRIVERS (INVERSORES DE FREQUÊNCIA E SOFT-STATERS), ABRANGENDO FORNECIMENTO DE PEÇAS, MÃO DE OBRA ESPECIALIZADA</t>
+  </si>
+  <si>
+    <t>GOLD MAQUINAS ELETRICAS INDUSTRIAIS LTDA-ME</t>
+  </si>
+  <si>
+    <t>00000006/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        658999,61</t>
+  </si>
+  <si>
+    <t>SERVIÇOS DE EXECUÇÃO CONTINUADA PARA FABRICAÇÃO E INSTALAÇÃO DE TAMPAS EM POLIETILENO 6MM DE ALTA DENSIDADE, ARREBITES DE ALUMÍNIO 6MM MEDIDA 6,2X19 E CANTONEIRA GALVANIZADA A QUENTE DE 11/2X1/8 E GRADES EM FERRO REDONDO DE 12MM EM AÇO INOX</t>
+  </si>
+  <si>
+    <t>GENTIL APOLINARIO DE SOUZA - ME</t>
+  </si>
+  <si>
+    <t>00000005/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       4121604,03</t>
+  </si>
+  <si>
+    <t>30/07/2026</t>
+  </si>
+  <si>
+    <t>05/02/2025</t>
+  </si>
+  <si>
+    <t>06/02/2024</t>
+  </si>
+  <si>
+    <t>EXECUÇÃO DE 04 (QUATRO) POÇOS TUBULARES PROFUNDOS, COM A DEVIDA APLICAÇÃO DE MATERIAIS NO MUNICÍPIO DE RONDONÓPOLIS – MT</t>
+  </si>
+  <si>
+    <t>MILLENIUM INDUSTRIA COMERCIO DE IMPORTACAO E EXP. DE ARTEFATOS DE CIMENTO LTDA</t>
+  </si>
+  <si>
+    <t>00000000008/2026</t>
+  </si>
+  <si>
+    <t>00000003/2024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       3690835,63</t>
+  </si>
+  <si>
+    <t>31/07/2026</t>
+  </si>
+  <si>
+    <t>31/07/2024</t>
+  </si>
+  <si>
+    <t>01/08/2023</t>
+  </si>
+  <si>
+    <t>SERVIÇOS DE PUBLICIDADE, ENVOLVENDO AS SEGUINTES ATIVIDADES PROFISSIONAIS: ESTUDO, PLANEJAMENTO, CONCEITUAÇÃO, CONCEPÇÃO, CRIAÇÃO, EXECUÇÃO INTERNA, INTERMEDIAÇÃO, SUPERVISÃO DA EXECUÇÃO EXTERNA E A DISTRIBUIÇÃO DE PUBLICIDADE</t>
+  </si>
+  <si>
+    <t>J.V. FERMINO DA SILVA</t>
+  </si>
+  <si>
+    <t>00000000004/2025</t>
+  </si>
+  <si>
+    <t>00000015/2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         16500,00</t>
+  </si>
+  <si>
+    <t>09/07/2026</t>
+  </si>
+  <si>
+    <t>09/01/2026</t>
+  </si>
+  <si>
+    <t>10/09/2025</t>
+  </si>
+  <si>
+    <t>CONTRATO DE LOCAÇÃO DE IMÓVEL</t>
+  </si>
+  <si>
+    <t>NOEL CAVALCANTE PAZ</t>
+  </si>
+  <si>
+    <t>00000000001/2026</t>
+  </si>
+  <si>
+    <t>00000011/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        474666,67</t>
+  </si>
+  <si>
+    <t>27/07/2026</t>
+  </si>
+  <si>
+    <t>27/11/2023</t>
+  </si>
+  <si>
+    <t>28/11/2022</t>
+  </si>
+  <si>
+    <t>AQUISIÇÃO DE SERVIÇO DE MANUTENÇÃO PREVENTIVA E CORRETIVA EM VEÍCULOS AUTOMOTORES, COM FORNECIMENTO DE PEÇAS DE REPOSIÇÃO E ACESSÓRIOS ORIGINAIS, GENUÍNOS OU SIMILARES QUE ATENDAM ÀS RECOMENDAÇÕES DOS FABRICANTES PARA A FROTA DE VEÍCULOS OFICIAIS DO SANEA</t>
+  </si>
+  <si>
+    <t>MOTOFORT COM. VAREJO DE PECAS E SERVICO LTDA - EPP</t>
+  </si>
+  <si>
+    <t>00000000003/2025</t>
+  </si>
+  <si>
+    <t>00000036/2022</t>
   </si>
 </sst>
 </file>
@@ -502,6 +647,228 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3DAA10-5549-46D7-8BC7-FCD302E7A20A}">
+  <dimension ref="A1:H8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="3" max="3" width="39.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C2" t="s">
+        <v>89</v>
+      </c>
+      <c r="D2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F2" t="s">
+        <v>86</v>
+      </c>
+      <c r="G2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B3" t="s">
+        <v>82</v>
+      </c>
+      <c r="C3" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3" t="s">
+        <v>79</v>
+      </c>
+      <c r="F3" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>75</v>
+      </c>
+      <c r="B4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" t="s">
+        <v>72</v>
+      </c>
+      <c r="E4" t="s">
+        <v>71</v>
+      </c>
+      <c r="F4" t="s">
+        <v>70</v>
+      </c>
+      <c r="G4" t="s">
+        <v>69</v>
+      </c>
+      <c r="H4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>66</v>
+      </c>
+      <c r="C5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D5" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" t="s">
+        <v>63</v>
+      </c>
+      <c r="F5" t="s">
+        <v>62</v>
+      </c>
+      <c r="G5" t="s">
+        <v>61</v>
+      </c>
+      <c r="H5" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>59</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" t="s">
+        <v>51</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>54</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s">
+        <v>52</v>
+      </c>
+      <c r="F7" t="s">
+        <v>51</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>49</v>
+      </c>
+      <c r="B8" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" t="s">
+        <v>48</v>
+      </c>
+      <c r="D8" t="s">
+        <v>47</v>
+      </c>
+      <c r="E8" t="s">
+        <v>46</v>
+      </c>
+      <c r="F8" t="s">
+        <v>45</v>
+      </c>
+      <c r="G8" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" t="s">
+        <v>44</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/abril-2026.xlsx
+++ b/abril-2026.xlsx
@@ -8,20 +8,21 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E85F17DC-2C7B-4E09-B080-46A3A5CADAC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57326121-AF63-4D73-84F1-F4F25482E931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet0" sheetId="2" r:id="rId1"/>
-    <sheet name="Abril" sheetId="1" r:id="rId2"/>
+    <sheet name="Julho" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet0" sheetId="3" r:id="rId2"/>
+    <sheet name="Abril" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="146">
   <si>
     <t>Contrato</t>
   </si>
@@ -297,6 +298,168 @@
   </si>
   <si>
     <t>00000036/2022</t>
+  </si>
+  <si>
+    <t>00000008/2023</t>
+  </si>
+  <si>
+    <t>SERVIÇO DE DIAGNÓSTICO SITUACIONAL INTERNO, ESTUDOS HIDROGEOLÓGICOS, SERVIÇOS DE LIMPEZA E MANUTENÇÃO DE POÇOS TUBULARES PROFUNDOS</t>
+  </si>
+  <si>
+    <t>08/05/2023</t>
+  </si>
+  <si>
+    <t>06/05/2024</t>
+  </si>
+  <si>
+    <t>04/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       1496880,00</t>
+  </si>
+  <si>
+    <t>00000009/2023</t>
+  </si>
+  <si>
+    <t>EXECUÇÃO DE 03 (TRES) POÇOS TUBULARES PROFUNDOS, COM A DEVIDA APLICAÇÃO DE MATERIAIS NO MUNICÍPIO DE RONDONÓPOLIS – MT</t>
+  </si>
+  <si>
+    <t>27/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       1943588,94</t>
+  </si>
+  <si>
+    <t>00000016/2023</t>
+  </si>
+  <si>
+    <t>COOMSER - COOPERTIVA DE TRABALHO E SERVIÇOS  DE RONDONÓPOLIS</t>
+  </si>
+  <si>
+    <t>SERVIÇOS DE OPERAÇÕES COMERCIAIS E ADMINISTRATIVAS</t>
+  </si>
+  <si>
+    <t>02/08/2023</t>
+  </si>
+  <si>
+    <t>01/08/2024</t>
+  </si>
+  <si>
+    <t>01/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">      88196043,66</t>
+  </si>
+  <si>
+    <t>00000017/2023</t>
+  </si>
+  <si>
+    <t>EBARA BOMBAS AMERICA DO SUL LTDA</t>
+  </si>
+  <si>
+    <t>MANUTENÇÃO COM O FORNECIMENTO DE PEÇAS ORIGINAIS PARA CONJUNTOS MOTOBOMBAS SUBMERSÍVEIS E SUBMERSAS DA MARCA EBARA, COM TESTES DE CARGAS E FORNECIMENTO DOS LAUDOS TÉCNICOS</t>
+  </si>
+  <si>
+    <t>22/08/2023</t>
+  </si>
+  <si>
+    <t>21/08/2024</t>
+  </si>
+  <si>
+    <t>21/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       2398631,01</t>
+  </si>
+  <si>
+    <t>00000008/2025</t>
+  </si>
+  <si>
+    <t>IVECANIA MECANICA DIESEL LTDA</t>
+  </si>
+  <si>
+    <t>MANUTENÇÃO PREVENTIVA E CORRETIVA EM VEÍCULOS AUTOMOTORES, COM FORNECIMENTO DE PEÇAS DE REPOSIÇÃO E ACESSÓRIOS ORIGINAIS, GENUÍNOS</t>
+  </si>
+  <si>
+    <t>04/08/2025</t>
+  </si>
+  <si>
+    <t>03/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        993750,00</t>
+  </si>
+  <si>
+    <t>00000009/2025</t>
+  </si>
+  <si>
+    <t>TECNOBOMBAS - BOMBAS MOTORES E SERVICOS LTDA</t>
+  </si>
+  <si>
+    <t>MANUTENÇÃO PREVENTIVA E CORRETIVA EM MOTORES ELÉTRICOS COMUNS, ABRANGENDO FORNECIMENTO DE PEÇAS, MÃO DE OBRA ESPECIALIZADA</t>
+  </si>
+  <si>
+    <t>18/08/2025</t>
+  </si>
+  <si>
+    <t>17/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">       1404000,00</t>
+  </si>
+  <si>
+    <t>00000014/2024</t>
+  </si>
+  <si>
+    <t>COOPERATIVA DE MATERIAIS RECICLADOS PE. LOTHAR BAUCHROWITZ - COOPERCICLA</t>
+  </si>
+  <si>
+    <t>CONTRATAÇÃO DE COOPERATIVA DE CATADORES DE MATERIAIS RECICLÁVEIS, EM CARÁTER CONTINUADO, PARA A OPERACIONALIZAÇÃO DO PROCESSO DE SEPARAÇÃO E COMERCIALIZAÇÃO DOS RESÍDUOS RECICLÁVEIS ORIUNDOS DA COLETA SELETIVA</t>
+  </si>
+  <si>
+    <t>27/08/2024</t>
+  </si>
+  <si>
+    <t>26/08/2025</t>
+  </si>
+  <si>
+    <t>26/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        483120,00</t>
+  </si>
+  <si>
+    <t>00000007/2026</t>
+  </si>
+  <si>
+    <t>J. C. RODRIGUES JUNIOR</t>
+  </si>
+  <si>
+    <t>PRESTAÇÃO DE SERVIÇOS DE DEDETIZAÇÃO, DESRATIZAÇÃO E CONTROLE DE POMBOS NAS DEPENDÊNCIAS DA AGÊNCIA CENTRO E AGÊNCIA MONTE LÍBANO DO SANEAR</t>
+  </si>
+  <si>
+    <t>13/05/2026</t>
+  </si>
+  <si>
+    <t>10/08/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         40400,00</t>
+  </si>
+  <si>
+    <t>00000010/2026</t>
+  </si>
+  <si>
+    <t>WM ESTUDOS E CONSULTORIA LTDA</t>
+  </si>
+  <si>
+    <t>SERVIÇOS ESPECIALIZADOS DE ENGENHARIA CONSULTIVA PARA ELABORAÇÃO DE ESTUDOS TÉCNICOS, DIMENSIONAMENTOS   E PROJETOS EXECUTIVOS VOLTADOS À REESTRUTURAÇÃO DA CÂMARA DE SUCÇÃO  E BARRILETES DA ESTAÇÃO ELEVATÓRIA DE ÁGUA BRUTA 2 (EEAB2)</t>
+  </si>
+  <si>
+    <t>20/05/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">         59200,00</t>
   </si>
 </sst>
 </file>
@@ -651,7 +814,8 @@
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="17.28515625" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" customWidth="1"/>
+    <col min="2" max="2" width="19.5703125" customWidth="1"/>
     <col min="3" max="3" width="39.140625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -869,6 +1033,276 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D547F0B-59C9-4025-BEC9-C86F17EEFD09}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" t="s">
+        <v>132</v>
+      </c>
+      <c r="G8" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/abril-2026.xlsx
+++ b/abril-2026.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57326121-AF63-4D73-84F1-F4F25482E931}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5E171A7-B88F-459D-ACBD-FBBA191C6006}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Julho" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet0" sheetId="3" r:id="rId2"/>
+    <sheet name="Sheet0" sheetId="3" r:id="rId1"/>
+    <sheet name="Julho" sheetId="2" r:id="rId2"/>
     <sheet name="Abril" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
@@ -810,6 +810,276 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D547F0B-59C9-4025-BEC9-C86F17EEFD09}">
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>92</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E2" t="s">
+        <v>94</v>
+      </c>
+      <c r="F2" t="s">
+        <v>95</v>
+      </c>
+      <c r="G2" t="s">
+        <v>96</v>
+      </c>
+      <c r="H2" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D3" t="s">
+        <v>99</v>
+      </c>
+      <c r="E3" t="s">
+        <v>94</v>
+      </c>
+      <c r="F3" t="s">
+        <v>95</v>
+      </c>
+      <c r="G3" t="s">
+        <v>100</v>
+      </c>
+      <c r="H3" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>102</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>103</v>
+      </c>
+      <c r="D4" t="s">
+        <v>104</v>
+      </c>
+      <c r="E4" t="s">
+        <v>105</v>
+      </c>
+      <c r="F4" t="s">
+        <v>106</v>
+      </c>
+      <c r="G4" t="s">
+        <v>107</v>
+      </c>
+      <c r="H4" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>109</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" t="s">
+        <v>110</v>
+      </c>
+      <c r="D5" t="s">
+        <v>111</v>
+      </c>
+      <c r="E5" t="s">
+        <v>112</v>
+      </c>
+      <c r="F5" t="s">
+        <v>113</v>
+      </c>
+      <c r="G5" t="s">
+        <v>114</v>
+      </c>
+      <c r="H5" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>116</v>
+      </c>
+      <c r="B6" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" t="s">
+        <v>117</v>
+      </c>
+      <c r="D6" t="s">
+        <v>118</v>
+      </c>
+      <c r="E6" t="s">
+        <v>119</v>
+      </c>
+      <c r="F6" t="s">
+        <v>120</v>
+      </c>
+      <c r="G6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" t="s">
+        <v>125</v>
+      </c>
+      <c r="F7" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" t="s">
+        <v>25</v>
+      </c>
+      <c r="H7" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>128</v>
+      </c>
+      <c r="B8" t="s">
+        <v>32</v>
+      </c>
+      <c r="C8" t="s">
+        <v>129</v>
+      </c>
+      <c r="D8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" t="s">
+        <v>131</v>
+      </c>
+      <c r="F8" t="s">
+        <v>132</v>
+      </c>
+      <c r="G8" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" t="s">
+        <v>136</v>
+      </c>
+      <c r="D9" t="s">
+        <v>137</v>
+      </c>
+      <c r="E9" t="s">
+        <v>138</v>
+      </c>
+      <c r="F9" t="s">
+        <v>139</v>
+      </c>
+      <c r="G9" t="s">
+        <v>25</v>
+      </c>
+      <c r="H9" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10" t="s">
+        <v>25</v>
+      </c>
+      <c r="C10" t="s">
+        <v>142</v>
+      </c>
+      <c r="D10" t="s">
+        <v>143</v>
+      </c>
+      <c r="E10" t="s">
+        <v>144</v>
+      </c>
+      <c r="F10" t="s">
+        <v>126</v>
+      </c>
+      <c r="G10" t="s">
+        <v>25</v>
+      </c>
+      <c r="H10" t="s">
+        <v>145</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4A3DAA10-5549-46D7-8BC7-FCD302E7A20A}">
   <dimension ref="A1:H8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1029,276 +1299,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7D547F0B-59C9-4025-BEC9-C86F17EEFD09}">
-  <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>92</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E2" t="s">
-        <v>94</v>
-      </c>
-      <c r="F2" t="s">
-        <v>95</v>
-      </c>
-      <c r="G2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B3" t="s">
-        <v>66</v>
-      </c>
-      <c r="C3" t="s">
-        <v>65</v>
-      </c>
-      <c r="D3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E3" t="s">
-        <v>94</v>
-      </c>
-      <c r="F3" t="s">
-        <v>95</v>
-      </c>
-      <c r="G3" t="s">
-        <v>100</v>
-      </c>
-      <c r="H3" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>102</v>
-      </c>
-      <c r="B4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>103</v>
-      </c>
-      <c r="D4" t="s">
-        <v>104</v>
-      </c>
-      <c r="E4" t="s">
-        <v>105</v>
-      </c>
-      <c r="F4" t="s">
-        <v>106</v>
-      </c>
-      <c r="G4" t="s">
-        <v>107</v>
-      </c>
-      <c r="H4" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>109</v>
-      </c>
-      <c r="B5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C5" t="s">
-        <v>110</v>
-      </c>
-      <c r="D5" t="s">
-        <v>111</v>
-      </c>
-      <c r="E5" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" t="s">
-        <v>113</v>
-      </c>
-      <c r="G5" t="s">
-        <v>114</v>
-      </c>
-      <c r="H5" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>116</v>
-      </c>
-      <c r="B6" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" t="s">
-        <v>117</v>
-      </c>
-      <c r="D6" t="s">
-        <v>118</v>
-      </c>
-      <c r="E6" t="s">
-        <v>119</v>
-      </c>
-      <c r="F6" t="s">
-        <v>120</v>
-      </c>
-      <c r="G6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H6" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" t="s">
-        <v>124</v>
-      </c>
-      <c r="E7" t="s">
-        <v>125</v>
-      </c>
-      <c r="F7" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" t="s">
-        <v>25</v>
-      </c>
-      <c r="H7" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>128</v>
-      </c>
-      <c r="B8" t="s">
-        <v>32</v>
-      </c>
-      <c r="C8" t="s">
-        <v>129</v>
-      </c>
-      <c r="D8" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" t="s">
-        <v>131</v>
-      </c>
-      <c r="F8" t="s">
-        <v>132</v>
-      </c>
-      <c r="G8" t="s">
-        <v>133</v>
-      </c>
-      <c r="H8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>135</v>
-      </c>
-      <c r="B9" t="s">
-        <v>25</v>
-      </c>
-      <c r="C9" t="s">
-        <v>136</v>
-      </c>
-      <c r="D9" t="s">
-        <v>137</v>
-      </c>
-      <c r="E9" t="s">
-        <v>138</v>
-      </c>
-      <c r="F9" t="s">
-        <v>139</v>
-      </c>
-      <c r="G9" t="s">
-        <v>25</v>
-      </c>
-      <c r="H9" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>141</v>
-      </c>
-      <c r="B10" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" t="s">
-        <v>142</v>
-      </c>
-      <c r="D10" t="s">
-        <v>143</v>
-      </c>
-      <c r="E10" t="s">
-        <v>144</v>
-      </c>
-      <c r="F10" t="s">
-        <v>126</v>
-      </c>
-      <c r="G10" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" t="s">
-        <v>145</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>
 
